--- a/src/odakyuPortal/test/downloads/Route Templates.xlsx
+++ b/src/odakyuPortal/test/downloads/Route Templates.xlsx
@@ -584,7 +584,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="4">
-        <x:v>46209.524853287</x:v>
+        <x:v>46224.5784588194</x:v>
       </x:c>
       <x:c r="C2" s="3"/>
       <x:c r="D2" s="3"/>
@@ -708,7 +708,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D11" s="6">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">

--- a/src/odakyuPortal/test/downloads/Route Templates.xlsx
+++ b/src/odakyuPortal/test/downloads/Route Templates.xlsx
@@ -584,7 +584,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="4">
-        <x:v>46224.5784588194</x:v>
+        <x:v>46226.4548371644</x:v>
       </x:c>
       <x:c r="C2" s="3"/>
       <x:c r="D2" s="3"/>
